--- a/data/trans_orig/IP31KM10_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM10_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>75575</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>64280</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>86752</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>55033</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46233</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>63474</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>48,17%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>79997</t>
+          <t>57714</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64568</t>
+          <t>48230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95082</t>
+          <t>67281</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>135030</t>
+          <t>133289</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119157</t>
+          <t>119019</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153098</t>
+          <t>149722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>62,0%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47321</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36144</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>58616</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>59218</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50777</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>68018</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>51,83%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56818</t>
+          <t>60884</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41733</t>
+          <t>51317</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72247</t>
+          <t>70368</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>116036</t>
+          <t>108205</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97968</t>
+          <t>91772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131909</t>
+          <t>122475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>151813</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>137798</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>163993</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>65,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>102915</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>90450</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>115223</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>55,3%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>48,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>61,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>156305</t>
+          <t>105615</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>141537</t>
+          <t>93844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170090</t>
+          <t>116886</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>259221</t>
+          <t>257427</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>239852</t>
+          <t>239823</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>279478</t>
+          <t>273447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>66,4%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79428</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>67248</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>93443</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>34,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>83199</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>70891</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>95664</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>44,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>38,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>51,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>91215</t>
+          <t>74978</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77430</t>
+          <t>63707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105983</t>
+          <t>86749</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>174413</t>
+          <t>154406</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154156</t>
+          <t>138386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193782</t>
+          <t>172010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>103736</t>
+          <t>81783</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84288</t>
+          <t>69545</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138413</t>
+          <t>94526</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89242</t>
+          <t>72769</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75534</t>
+          <t>61795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103724</t>
+          <t>83766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>192979</t>
+          <t>154552</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169026</t>
+          <t>138083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236828</t>
+          <t>171806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>84739</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71996</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>96977</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>58,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>84513</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>49836</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>103961</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>44,89%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>55,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93847</t>
+          <t>82269</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79365</t>
+          <t>71272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107555</t>
+          <t>93243</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>178360</t>
+          <t>167008</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134511</t>
+          <t>149754</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202313</t>
+          <t>183477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>57,06%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>87793</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>76815</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>99481</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>52,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>46,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>59,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>80705</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>70305</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>91447</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>42,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>94275</t>
+          <t>80684</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82385</t>
+          <t>70235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107667</t>
+          <t>92022</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>174980</t>
+          <t>168476</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157999</t>
+          <t>152942</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190772</t>
+          <t>184087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78372</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66684</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>89350</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>40,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>53,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>83814</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73072</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>94214</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>50,94%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>57,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>83034</t>
+          <t>83295</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69642</t>
+          <t>71957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94924</t>
+          <t>93744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>166848</t>
+          <t>161668</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151056</t>
+          <t>146057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183829</t>
+          <t>177202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>396963</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>372106</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>422138</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>57,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>61,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>459</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>342390</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>317176</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>383688</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>52,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>419820</t>
+          <t>316782</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>394361</t>
+          <t>296244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>449275</t>
+          <t>339309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>762210</t>
+          <t>713745</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>726618</t>
+          <t>683147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>811629</t>
+          <t>746073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>289861</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>264686</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>314718</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>38,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>310744</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>269446</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>335958</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>41,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>324913</t>
+          <t>301426</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>295458</t>
+          <t>278899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>350372</t>
+          <t>321964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>635657</t>
+          <t>591286</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>586238</t>
+          <t>558958</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>671249</t>
+          <t>621884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
